--- a/data/market_data.xlsx
+++ b/data/market_data.xlsx
@@ -2,13 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
-  <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pmoor\bob\tech_drawdown\data\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{532C5932-1714-420F-9555-1B99735A389D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <workbookPr filterPrivacy="1"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{41216CD5-40F1-4EF4-936D-1A6AEEDB684A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25392,6 +25387,7 @@
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -29947,6 +29943,7 @@
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -34437,6 +34434,7 @@
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -38867,6 +38865,7 @@
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -43333,6 +43332,7 @@
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -52208,5 +52208,275 @@
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=_xmlsignatures/sig1.xml><?xml version="1.0" encoding="utf-8"?>
+<Signature xmlns="http://www.w3.org/2000/09/xmldsig#" Id="idPackageSignature">
+  <SignedInfo>
+    <CanonicalizationMethod Algorithm="http://www.w3.org/TR/2001/REC-xml-c14n-20010315"/>
+    <SignatureMethod Algorithm="http://www.w3.org/2001/04/xmldsig-more#ecdsa-sha384"/>
+    <Reference Type="http://www.w3.org/2000/09/xmldsig#Object" URI="#idPackageObject">
+      <DigestMethod Algorithm="http://www.w3.org/2001/04/xmldsig-more#sha384"/>
+      <DigestValue>gJljjwLLfBR6Glm+ulyqoNWpiVliZnKaCVYkgJqsxhUxn4R5lloIir2tYZM5ntac</DigestValue>
+    </Reference>
+    <Reference Type="http://www.w3.org/2000/09/xmldsig#Object" URI="#idOfficeObject">
+      <DigestMethod Algorithm="http://www.w3.org/2001/04/xmldsig-more#sha384"/>
+      <DigestValue>ymV95A8Q+Bxp8EWZ/J6n/k0jnCZie3pua+KZnDPPxnW4WX+LPNnIsJGXkEdwKCiv</DigestValue>
+    </Reference>
+    <Reference Type="http://uri.etsi.org/01903#SignedProperties" URI="#idSignedProperties">
+      <Transforms>
+        <Transform Algorithm="http://www.w3.org/TR/2001/REC-xml-c14n-20010315"/>
+      </Transforms>
+      <DigestMethod Algorithm="http://www.w3.org/2001/04/xmldsig-more#sha384"/>
+      <DigestValue>LdclDErYfV5DA1Y1lNlbwufrJK82wC6JWioG8fb1BURnFQVQKp0KoRHSXLh/v7jX</DigestValue>
+    </Reference>
+  </SignedInfo>
+  <SignatureValue>72t5nO49KLy6XBcH/qe1PMcwSq00uReULWCxjLiuQyTJJF1F9AE3EHCBtw189WfXVLnkGhapY3zK
+xVUmpr7n58wPsitmZmX0S8Jc0cZjZI7XS4B71aARlYUPxbmHm5dd</SignatureValue>
+  <KeyInfo>
+    <X509Data>
+      <X509Certificate>MIIBkTCCARagAwIBAgIJAPdIHSGNfZuUMAoGCCqGSM49BAMDMC8xLTArBgNVBAMTJGNhYTIyY2YxLWMxM2YtNDM3Yy1iYWZkLWFhNjM5MjU5MDkzMTAeFw0yNjAzMDgwMTU2MzlaFw0yNzAzMDgxMzU2MzlaMC8xLTArBgNVBAMTJGNhYTIyY2YxLWMxM2YtNDM3Yy1iYWZkLWFhNjM5MjU5MDkzMTB2MBAGByqGSM49AgEGBSuBBAAiA2IABNp6f9pfSrQcXKO+mGODiKCBvrFCgM6z6svOeFdn85eIZkMNYGiGy4qv372dsw6lUyYdMetE51bq0gc2taRfqpv74xATA8+srJCgSRF8wKRuy54sgtL8WciTs1VhOPHsaTAKBggqhkjOPQQDAwNpADBmAjEA5hZTKtauY9KNCFdXK5ZSsXmnIrEb3vm1m+GkTPdKWTDFsKMxe03DPvyHL6v5vvpnAjEAsDyuNkP5luWjdar8Nfd6yIN8WevzfJxqjLpxnT0OFiseNRTv1Xfsu9jmilU9jePZ</X509Certificate>
+    </X509Data>
+  </KeyInfo>
+  <Object Id="idPackageObject">
+    <Manifest>
+      <Reference URI="/_rels/.rels?ContentType=application/vnd.openxmlformats-package.relationships+xml">
+        <Transforms>
+          <Transform Algorithm="http://schemas.openxmlformats.org/package/2006/RelationshipTransform">
+            <mdssi:RelationshipReference xmlns:mdssi="http://schemas.openxmlformats.org/package/2006/digital-signature" SourceId="rId1"/>
+          </Transform>
+          <Transform Algorithm="http://www.w3.org/TR/2001/REC-xml-c14n-20010315"/>
+        </Transforms>
+        <DigestMethod Algorithm="http://www.w3.org/2001/04/xmldsig-more#sha384"/>
+        <DigestValue>Mf2/mKvHoEm+XQe0V5FnG8+mCC19i1rJCIQNslrm4nmnCLDlck67lEpi2D8bIPxk</DigestValue>
+      </Reference>
+      <Reference URI="/xl/_rels/workbook.xml.rels?ContentType=application/vnd.openxmlformats-package.relationships+xml">
+        <Transforms>
+          <Transform Algorithm="http://schemas.openxmlformats.org/package/2006/RelationshipTransform">
+            <mdssi:RelationshipReference xmlns:mdssi="http://schemas.openxmlformats.org/package/2006/digital-signature" SourceId="rId7"/>
+            <mdssi:RelationshipReference xmlns:mdssi="http://schemas.openxmlformats.org/package/2006/digital-signature" SourceId="rId2"/>
+            <mdssi:RelationshipReference xmlns:mdssi="http://schemas.openxmlformats.org/package/2006/digital-signature" SourceId="rId1"/>
+            <mdssi:RelationshipReference xmlns:mdssi="http://schemas.openxmlformats.org/package/2006/digital-signature" SourceId="rId6"/>
+            <mdssi:RelationshipReference xmlns:mdssi="http://schemas.openxmlformats.org/package/2006/digital-signature" SourceId="rId5"/>
+            <mdssi:RelationshipReference xmlns:mdssi="http://schemas.openxmlformats.org/package/2006/digital-signature" SourceId="rId4"/>
+            <mdssi:RelationshipReference xmlns:mdssi="http://schemas.openxmlformats.org/package/2006/digital-signature" SourceId="rId9"/>
+            <mdssi:RelationshipReference xmlns:mdssi="http://schemas.openxmlformats.org/package/2006/digital-signature" SourceId="rId8"/>
+            <mdssi:RelationshipReference xmlns:mdssi="http://schemas.openxmlformats.org/package/2006/digital-signature" SourceId="rId3"/>
+          </Transform>
+          <Transform Algorithm="http://www.w3.org/TR/2001/REC-xml-c14n-20010315"/>
+        </Transforms>
+        <DigestMethod Algorithm="http://www.w3.org/2001/04/xmldsig-more#sha384"/>
+        <DigestValue>fLbcDyKAODj347/HMCp2zqIMH6o1RQfZi1zY6Ny7LqRE+e+jZUYdXCITaX3ykM+y</DigestValue>
+      </Reference>
+      <Reference URI="/xl/printerSettings/printerSettings1.bin?ContentType=application/vnd.openxmlformats-officedocument.spreadsheetml.printerSettings">
+        <DigestMethod Algorithm="http://www.w3.org/2001/04/xmldsig-more#sha384"/>
+        <DigestValue>jdkovzPyoW4YdRFtaFj9zLX3JL9qQ9CaJjWN7SKRLNROM+ExwfDSVlVw14wBipYQ</DigestValue>
+      </Reference>
+      <Reference URI="/xl/printerSettings/printerSettings2.bin?ContentType=application/vnd.openxmlformats-officedocument.spreadsheetml.printerSettings">
+        <DigestMethod Algorithm="http://www.w3.org/2001/04/xmldsig-more#sha384"/>
+        <DigestValue>jdkovzPyoW4YdRFtaFj9zLX3JL9qQ9CaJjWN7SKRLNROM+ExwfDSVlVw14wBipYQ</DigestValue>
+      </Reference>
+      <Reference URI="/xl/printerSettings/printerSettings3.bin?ContentType=application/vnd.openxmlformats-officedocument.spreadsheetml.printerSettings">
+        <DigestMethod Algorithm="http://www.w3.org/2001/04/xmldsig-more#sha384"/>
+        <DigestValue>jdkovzPyoW4YdRFtaFj9zLX3JL9qQ9CaJjWN7SKRLNROM+ExwfDSVlVw14wBipYQ</DigestValue>
+      </Reference>
+      <Reference URI="/xl/printerSettings/printerSettings4.bin?ContentType=application/vnd.openxmlformats-officedocument.spreadsheetml.printerSettings">
+        <DigestMethod Algorithm="http://www.w3.org/2001/04/xmldsig-more#sha384"/>
+        <DigestValue>jdkovzPyoW4YdRFtaFj9zLX3JL9qQ9CaJjWN7SKRLNROM+ExwfDSVlVw14wBipYQ</DigestValue>
+      </Reference>
+      <Reference URI="/xl/printerSettings/printerSettings5.bin?ContentType=application/vnd.openxmlformats-officedocument.spreadsheetml.printerSettings">
+        <DigestMethod Algorithm="http://www.w3.org/2001/04/xmldsig-more#sha384"/>
+        <DigestValue>jdkovzPyoW4YdRFtaFj9zLX3JL9qQ9CaJjWN7SKRLNROM+ExwfDSVlVw14wBipYQ</DigestValue>
+      </Reference>
+      <Reference URI="/xl/printerSettings/printerSettings6.bin?ContentType=application/vnd.openxmlformats-officedocument.spreadsheetml.printerSettings">
+        <DigestMethod Algorithm="http://www.w3.org/2001/04/xmldsig-more#sha384"/>
+        <DigestValue>jdkovzPyoW4YdRFtaFj9zLX3JL9qQ9CaJjWN7SKRLNROM+ExwfDSVlVw14wBipYQ</DigestValue>
+      </Reference>
+      <Reference URI="/xl/sharedStrings.xml?ContentType=application/vnd.openxmlformats-officedocument.spreadsheetml.sharedStrings+xml">
+        <DigestMethod Algorithm="http://www.w3.org/2001/04/xmldsig-more#sha384"/>
+        <DigestValue>oRq/+9s3/Z45K99wMaFt3KNKCIDkIoqOOLEiikWNUk5BR6h3+zW7ibmPpRrrKO46</DigestValue>
+      </Reference>
+      <Reference URI="/xl/styles.xml?ContentType=application/vnd.openxmlformats-officedocument.spreadsheetml.styles+xml">
+        <DigestMethod Algorithm="http://www.w3.org/2001/04/xmldsig-more#sha384"/>
+        <DigestValue>SmsiG8Zr5r3iPm53CNuAm1x4LvjEGQ7TmP/2ja8IfWBP1YEeNi4jJQqSZ1403aHc</DigestValue>
+      </Reference>
+      <Reference URI="/xl/theme/theme1.xml?ContentType=application/vnd.openxmlformats-officedocument.theme+xml">
+        <DigestMethod Algorithm="http://www.w3.org/2001/04/xmldsig-more#sha384"/>
+        <DigestValue>sk95Wr3Y9TnWspgLHC9yl6kALVIYVx0KvrYClrD17h9YO/eZw/efvx3510HNOeQZ</DigestValue>
+      </Reference>
+      <Reference URI="/xl/workbook.xml?ContentType=application/vnd.openxmlformats-officedocument.spreadsheetml.sheet.main+xml">
+        <DigestMethod Algorithm="http://www.w3.org/2001/04/xmldsig-more#sha384"/>
+        <DigestValue>pZLor11MJJohkQE66dWbVUXsAMQ+t3MI6rrLf9OvbNgasz4g/eWcNH/cLjSq01lh</DigestValue>
+      </Reference>
+      <Reference URI="/xl/worksheets/_rels/sheet1.xml.rels?ContentType=application/vnd.openxmlformats-package.relationships+xml">
+        <Transforms>
+          <Transform Algorithm="http://schemas.openxmlformats.org/package/2006/RelationshipTransform">
+            <mdssi:RelationshipReference xmlns:mdssi="http://schemas.openxmlformats.org/package/2006/digital-signature" SourceId="rId1"/>
+          </Transform>
+          <Transform Algorithm="http://www.w3.org/TR/2001/REC-xml-c14n-20010315"/>
+        </Transforms>
+        <DigestMethod Algorithm="http://www.w3.org/2001/04/xmldsig-more#sha384"/>
+        <DigestValue>xZOcSD7V2VTN15hVi8eyrnaBEr1zDrGJFmZUfNxcc43GC6P/kOI/8RwGSvRYJ7rg</DigestValue>
+      </Reference>
+      <Reference URI="/xl/worksheets/_rels/sheet2.xml.rels?ContentType=application/vnd.openxmlformats-package.relationships+xml">
+        <Transforms>
+          <Transform Algorithm="http://schemas.openxmlformats.org/package/2006/RelationshipTransform">
+            <mdssi:RelationshipReference xmlns:mdssi="http://schemas.openxmlformats.org/package/2006/digital-signature" SourceId="rId1"/>
+          </Transform>
+          <Transform Algorithm="http://www.w3.org/TR/2001/REC-xml-c14n-20010315"/>
+        </Transforms>
+        <DigestMethod Algorithm="http://www.w3.org/2001/04/xmldsig-more#sha384"/>
+        <DigestValue>yUmahslBWmqBB82Uv2hV0/qdNKQA+6OxraqyQ1pljHt0yqrM2IrmA5qiN4AsvWw9</DigestValue>
+      </Reference>
+      <Reference URI="/xl/worksheets/_rels/sheet3.xml.rels?ContentType=application/vnd.openxmlformats-package.relationships+xml">
+        <Transforms>
+          <Transform Algorithm="http://schemas.openxmlformats.org/package/2006/RelationshipTransform">
+            <mdssi:RelationshipReference xmlns:mdssi="http://schemas.openxmlformats.org/package/2006/digital-signature" SourceId="rId1"/>
+          </Transform>
+          <Transform Algorithm="http://www.w3.org/TR/2001/REC-xml-c14n-20010315"/>
+        </Transforms>
+        <DigestMethod Algorithm="http://www.w3.org/2001/04/xmldsig-more#sha384"/>
+        <DigestValue>GA3BCW7ziz7VmoWLcTov63hAG5pjDCvBWUOr/h2WqYjQXUmWYKZJFiddTOBVUtnm</DigestValue>
+      </Reference>
+      <Reference URI="/xl/worksheets/_rels/sheet4.xml.rels?ContentType=application/vnd.openxmlformats-package.relationships+xml">
+        <Transforms>
+          <Transform Algorithm="http://schemas.openxmlformats.org/package/2006/RelationshipTransform">
+            <mdssi:RelationshipReference xmlns:mdssi="http://schemas.openxmlformats.org/package/2006/digital-signature" SourceId="rId1"/>
+          </Transform>
+          <Transform Algorithm="http://www.w3.org/TR/2001/REC-xml-c14n-20010315"/>
+        </Transforms>
+        <DigestMethod Algorithm="http://www.w3.org/2001/04/xmldsig-more#sha384"/>
+        <DigestValue>xB5hObJTEJdDGRNIe9v9pS3u73qt1HV1YLb5iFhqAqaSITE3sG3YiDM4bPv/Whal</DigestValue>
+      </Reference>
+      <Reference URI="/xl/worksheets/_rels/sheet5.xml.rels?ContentType=application/vnd.openxmlformats-package.relationships+xml">
+        <Transforms>
+          <Transform Algorithm="http://schemas.openxmlformats.org/package/2006/RelationshipTransform">
+            <mdssi:RelationshipReference xmlns:mdssi="http://schemas.openxmlformats.org/package/2006/digital-signature" SourceId="rId1"/>
+          </Transform>
+          <Transform Algorithm="http://www.w3.org/TR/2001/REC-xml-c14n-20010315"/>
+        </Transforms>
+        <DigestMethod Algorithm="http://www.w3.org/2001/04/xmldsig-more#sha384"/>
+        <DigestValue>PEOwa/zs2A/591waUljGVjDDYBCE6esLvu3Yc6yR96YHpA/W/DsqA2/ZR3JfZSEj</DigestValue>
+      </Reference>
+      <Reference URI="/xl/worksheets/_rels/sheet6.xml.rels?ContentType=application/vnd.openxmlformats-package.relationships+xml">
+        <Transforms>
+          <Transform Algorithm="http://schemas.openxmlformats.org/package/2006/RelationshipTransform">
+            <mdssi:RelationshipReference xmlns:mdssi="http://schemas.openxmlformats.org/package/2006/digital-signature" SourceId="rId1"/>
+          </Transform>
+          <Transform Algorithm="http://www.w3.org/TR/2001/REC-xml-c14n-20010315"/>
+        </Transforms>
+        <DigestMethod Algorithm="http://www.w3.org/2001/04/xmldsig-more#sha384"/>
+        <DigestValue>Bq4/Jem35YHd5SHGkuf3eusSeFubaznHgCWrYyEB1X4zUzSSTKQAsnbBQdnQdSIL</DigestValue>
+      </Reference>
+      <Reference URI="/xl/worksheets/sheet1.xml?ContentType=application/vnd.openxmlformats-officedocument.spreadsheetml.worksheet+xml">
+        <DigestMethod Algorithm="http://www.w3.org/2001/04/xmldsig-more#sha384"/>
+        <DigestValue>oxMJoyswh8gT0rcCtff9GJGu8lM69AkbaC7G95cV/xmjqo3U6VnevXILWfM7OZxj</DigestValue>
+      </Reference>
+      <Reference URI="/xl/worksheets/sheet2.xml?ContentType=application/vnd.openxmlformats-officedocument.spreadsheetml.worksheet+xml">
+        <DigestMethod Algorithm="http://www.w3.org/2001/04/xmldsig-more#sha384"/>
+        <DigestValue>Khi/mpsYQGob73upQcau+I0wquSWP3pNkLwgf1qPc5WZzoDFqpGeQ6MBVuf0gHr4</DigestValue>
+      </Reference>
+      <Reference URI="/xl/worksheets/sheet3.xml?ContentType=application/vnd.openxmlformats-officedocument.spreadsheetml.worksheet+xml">
+        <DigestMethod Algorithm="http://www.w3.org/2001/04/xmldsig-more#sha384"/>
+        <DigestValue>5W3ebeFt3JfdHWpIBGA8Io7h3scJJWVIZlj05FeJaZMZxz33v8f8fLPQmZZd9STH</DigestValue>
+      </Reference>
+      <Reference URI="/xl/worksheets/sheet4.xml?ContentType=application/vnd.openxmlformats-officedocument.spreadsheetml.worksheet+xml">
+        <DigestMethod Algorithm="http://www.w3.org/2001/04/xmldsig-more#sha384"/>
+        <DigestValue>3KxUaRgeRz8/N356hIqH8kfRJRovDJGxB6zgevOnItVZPEYqChjPDHxLYqSiewO4</DigestValue>
+      </Reference>
+      <Reference URI="/xl/worksheets/sheet5.xml?ContentType=application/vnd.openxmlformats-officedocument.spreadsheetml.worksheet+xml">
+        <DigestMethod Algorithm="http://www.w3.org/2001/04/xmldsig-more#sha384"/>
+        <DigestValue>a/j3/JychkeXY9mB0DEaXgF+WUmnmzyk2nY6nS3Dmi+8IKw7uTMERRtrpbpt5N9w</DigestValue>
+      </Reference>
+      <Reference URI="/xl/worksheets/sheet6.xml?ContentType=application/vnd.openxmlformats-officedocument.spreadsheetml.worksheet+xml">
+        <DigestMethod Algorithm="http://www.w3.org/2001/04/xmldsig-more#sha384"/>
+        <DigestValue>+Mz+SjJZWsi7mPyyFNiOCvf5Dkn2OKxnFcAGhz+fa+UZVEjKkIbiVKyUr6HVpjbQ</DigestValue>
+      </Reference>
+    </Manifest>
+    <SignatureProperties>
+      <SignatureProperty Id="idSignatureTime" Target="#idPackageSignature">
+        <mdssi:SignatureTime xmlns:mdssi="http://schemas.openxmlformats.org/package/2006/digital-signature">
+          <mdssi:Format>YYYY-MM-DDThh:mm:ssTZD</mdssi:Format>
+          <mdssi:Value>2026-08-29T16:44:09Z</mdssi:Value>
+        </mdssi:SignatureTime>
+      </SignatureProperty>
+    </SignatureProperties>
+  </Object>
+  <Object Id="idOfficeObject">
+    <SignatureProperties>
+      <SignatureProperty Id="idOfficeV1Details" Target="#idPackageSignature">
+        <SignatureInfoV1 xmlns="http://schemas.microsoft.com/office/2006/digsig">
+          <SetupID/>
+          <SignatureText/>
+          <SignatureImage/>
+          <SignatureComments>Submission for IBM review</SignatureComments>
+          <WindowsVersion>10.0</WindowsVersion>
+          <OfficeVersion>16.0.20326/27</OfficeVersion>
+          <ApplicationVersion>16.0.20326</ApplicationVersion>
+          <Monitors>1</Monitors>
+          <HorizontalResolution>1920</HorizontalResolution>
+          <VerticalResolution>1080</VerticalResolution>
+          <ColorDepth>32</ColorDepth>
+          <SignatureProviderId>{00000000-0000-0000-0000-000000000000}</SignatureProviderId>
+          <SignatureProviderUrl/>
+          <SignatureProviderDetails>9</SignatureProviderDetails>
+          <SignatureType>1</SignatureType>
+        </SignatureInfoV1>
+        <SignatureInfoV2 xmlns="http://schemas.microsoft.com/office/2006/digsig">
+          <Address1/>
+          <Address2/>
+        </SignatureInfoV2>
+      </SignatureProperty>
+    </SignatureProperties>
+  </Object>
+  <Object>
+    <xd:QualifyingProperties xmlns:xd="http://uri.etsi.org/01903/v1.3.2#" Target="#idPackageSignature">
+      <xd:SignedProperties Id="idSignedProperties">
+        <xd:SignedSignatureProperties>
+          <xd:SigningTime>2026-08-29T16:44:09Z</xd:SigningTime>
+          <xd:SigningCertificate>
+            <xd:Cert>
+              <xd:CertDigest>
+                <DigestMethod Algorithm="http://www.w3.org/2001/04/xmldsig-more#sha384"/>
+                <DigestValue>AAGwLZ0Mju8BR7lCmJFzSejv/Gfu6+ToSzLGusuNTd9Nzga1YrQDdyDar9Vdx84e</DigestValue>
+              </xd:CertDigest>
+              <xd:IssuerSerial>
+                <X509IssuerName>CN=caa22cf1-c13f-437c-bafd-aa6392590931</X509IssuerName>
+                <X509SerialNumber>17818523955636312980</X509SerialNumber>
+              </xd:IssuerSerial>
+            </xd:Cert>
+          </xd:SigningCertificate>
+          <xd:SignaturePolicyIdentifier>
+            <xd:SignaturePolicyImplied/>
+          </xd:SignaturePolicyIdentifier>
+          <xd:SignatureProductionPlace>
+            <xd:City/>
+            <xd:StateOrProvince/>
+            <xd:PostalCode/>
+            <xd:CountryName/>
+          </xd:SignatureProductionPlace>
+          <xd:SignerRole>
+            <xd:ClaimedRoles>
+              <xd:ClaimedRole>Author</xd:ClaimedRole>
+            </xd:ClaimedRoles>
+          </xd:SignerRole>
+        </xd:SignedSignatureProperties>
+        <xd:SignedDataObjectProperties>
+          <xd:CommitmentTypeIndication>
+            <xd:CommitmentTypeId>
+              <xd:Identifier>http://uri.etsi.org/01903/v1.2.2#ProofOfOrigin</xd:Identifier>
+              <xd:Description>Created and approved this document</xd:Description>
+            </xd:CommitmentTypeId>
+            <xd:AllSignedDataObjects/>
+            <xd:CommitmentTypeQualifiers>
+              <xd:CommitmentTypeQualifier>Submission for IBM review</xd:CommitmentTypeQualifier>
+            </xd:CommitmentTypeQualifiers>
+          </xd:CommitmentTypeIndication>
+        </xd:SignedDataObjectProperties>
+      </xd:SignedProperties>
+    </xd:QualifyingProperties>
+  </Object>
+</Signature>
 </file>